--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20A94E2-CAA6-4F33-A1B0-05F42783FC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4B448A-D773-48D6-8DBA-37A6DE9FD8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="360">
   <si>
     <t>IZYgunT1ARCabineM608SurvivalRifle,items,gun,,,Model 608 Survival Rifle (T1),,,,,,,,,,,,,</t>
   </si>
@@ -550,9 +550,6 @@
   </si>
   <si>
     <t>not ready</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
   <si>
     <t>IZYgunT0SNIPERpipeAR15Broken15Junk</t>
@@ -1566,22 +1563,22 @@
         <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>137</v>
@@ -1596,19 +1593,19 @@
         <v>139</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="O1" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1619,10 +1616,10 @@
         <v>142</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>22</v>
@@ -1636,22 +1633,22 @@
         <v>141</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>23</v>
@@ -1660,7 +1657,7 @@
         <v>145</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>143</v>
@@ -1678,7 +1675,7 @@
         <v>groupWeaponsT0_Ranged</v>
       </c>
       <c r="Q3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1689,16 +1686,16 @@
         <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1709,22 +1706,22 @@
         <v>141</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>1</v>
@@ -1733,7 +1730,7 @@
         <v>145</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>146</v>
@@ -1751,7 +1748,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
       <c r="Q5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1762,16 +1759,16 @@
         <v>142</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>24</v>
       </c>
       <c r="Q6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1782,22 +1779,22 @@
         <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>25</v>
@@ -1806,7 +1803,7 @@
         <v>145</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>146</v>
@@ -1824,7 +1821,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
       <c r="Q7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1835,16 +1832,16 @@
         <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1855,22 +1852,22 @@
         <v>141</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>27</v>
@@ -1879,7 +1876,7 @@
         <v>145</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>146</v>
@@ -1897,7 +1894,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
       <c r="Q9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1908,19 +1905,19 @@
         <v>142</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1928,22 +1925,22 @@
         <v>141</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>29</v>
@@ -1952,7 +1949,7 @@
         <v>145</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>146</v>
@@ -1970,7 +1967,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
       <c r="Q11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1981,16 +1978,16 @@
         <v>142</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="Q12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2001,22 +1998,22 @@
         <v>141</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G13" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>31</v>
@@ -2025,7 +2022,7 @@
         <v>145</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>146</v>
@@ -2043,7 +2040,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
       <c r="Q13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2054,16 +2051,16 @@
         <v>142</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>32</v>
       </c>
       <c r="Q14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2074,22 +2071,22 @@
         <v>141</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G15" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>33</v>
@@ -2098,7 +2095,7 @@
         <v>145</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>146</v>
@@ -2116,7 +2113,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
       <c r="Q15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2127,16 +2124,16 @@
         <v>142</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="Q16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2147,22 +2144,22 @@
         <v>141</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>35</v>
@@ -2171,7 +2168,7 @@
         <v>145</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>143</v>
@@ -2189,7 +2186,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
       <c r="Q17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2200,16 +2197,16 @@
         <v>142</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="Q18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2220,22 +2217,22 @@
         <v>141</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>192</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>37</v>
@@ -2244,7 +2241,7 @@
         <v>145</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>146</v>
@@ -2262,7 +2259,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
       <c r="Q19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2273,19 +2270,19 @@
         <v>142</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="Q20" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2293,22 +2290,22 @@
         <v>141</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>39</v>
@@ -2317,7 +2314,7 @@
         <v>145</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>146</v>
@@ -2343,16 +2340,16 @@
         <v>142</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2360,22 +2357,22 @@
         <v>141</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>41</v>
@@ -2410,16 +2407,16 @@
         <v>142</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2427,22 +2424,22 @@
         <v>141</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>3</v>
@@ -2477,16 +2474,16 @@
         <v>142</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2494,22 +2491,22 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>5</v>
@@ -2544,16 +2541,16 @@
         <v>142</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -2561,22 +2558,22 @@
         <v>141</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G29" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>43</v>
@@ -2611,16 +2608,16 @@
         <v>142</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2628,22 +2625,22 @@
         <v>141</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G31" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>204</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>45</v>
@@ -2666,7 +2663,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P31" s="4" t="str">
         <f>D31 &amp; E31 &amp; "_" &amp; F31</f>
@@ -2681,10 +2678,10 @@
         <v>142</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>46</v>
@@ -2698,22 +2695,22 @@
         <v>141</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>47</v>
@@ -2736,7 +2733,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P33" s="4" t="str">
         <f>D33 &amp; E33 &amp; "_" &amp; F33</f>
@@ -2751,16 +2748,16 @@
         <v>142</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -2768,22 +2765,22 @@
         <v>141</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>49</v>
@@ -2818,16 +2815,16 @@
         <v>142</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2835,22 +2832,22 @@
         <v>141</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G37" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>210</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>51</v>
@@ -2885,16 +2882,16 @@
         <v>142</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2902,22 +2899,22 @@
         <v>141</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H39" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>53</v>
@@ -2940,7 +2937,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P39" s="4" t="str">
         <f>D39 &amp; E39 &amp; "_" &amp; F39</f>
@@ -2955,10 +2952,10 @@
         <v>142</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>54</v>
@@ -2972,22 +2969,22 @@
         <v>141</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>55</v>
@@ -3010,7 +3007,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P41" s="4" t="str">
         <f>D41 &amp; E41 &amp; "_" &amp; F41</f>
@@ -3025,16 +3022,16 @@
         <v>142</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -3042,22 +3039,22 @@
         <v>141</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G43" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>7</v>
@@ -3092,10 +3089,10 @@
         <v>142</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>56</v>
@@ -3109,22 +3106,22 @@
         <v>141</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>57</v>
@@ -3147,7 +3144,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P45" s="4" t="str">
         <f>D45 &amp; E45 &amp; "_" &amp; F45</f>
@@ -3162,10 +3159,10 @@
         <v>142</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>58</v>
@@ -3179,22 +3176,22 @@
         <v>141</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G47" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>59</v>
@@ -3203,7 +3200,7 @@
         <v>151</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>143</v>
@@ -3229,16 +3226,16 @@
         <v>142</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3246,22 +3243,22 @@
         <v>141</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G49" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>61</v>
@@ -3270,7 +3267,7 @@
         <v>151</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>143</v>
@@ -3296,10 +3293,10 @@
         <v>142</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>8</v>
@@ -3313,22 +3310,22 @@
         <v>141</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>9</v>
@@ -3337,7 +3334,7 @@
         <v>147</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>143</v>
@@ -3363,10 +3360,10 @@
         <v>142</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>62</v>
@@ -3380,22 +3377,22 @@
         <v>141</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>63</v>
@@ -3404,7 +3401,7 @@
         <v>147</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>143</v>
@@ -3430,16 +3427,16 @@
         <v>142</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -3447,22 +3444,22 @@
         <v>141</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G55" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>65</v>
@@ -3471,7 +3468,7 @@
         <v>147</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>143</v>
@@ -3497,10 +3494,10 @@
         <v>142</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>66</v>
@@ -3514,22 +3511,22 @@
         <v>141</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>67</v>
@@ -3538,7 +3535,7 @@
         <v>147</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>143</v>
@@ -3564,10 +3561,10 @@
         <v>142</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>68</v>
@@ -3581,22 +3578,22 @@
         <v>141</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>69</v>
@@ -3605,7 +3602,7 @@
         <v>147</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>143</v>
@@ -3631,16 +3628,16 @@
         <v>142</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -3648,22 +3645,22 @@
         <v>141</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>71</v>
@@ -3672,7 +3669,7 @@
         <v>147</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L61" s="4" t="s">
         <v>143</v>
@@ -3698,16 +3695,16 @@
         <v>142</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -3715,22 +3712,22 @@
         <v>141</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G63" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H63" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>73</v>
@@ -3739,7 +3736,7 @@
         <v>147</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L63" s="4" t="s">
         <v>143</v>
@@ -3765,10 +3762,10 @@
         <v>142</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>74</v>
@@ -3782,22 +3779,22 @@
         <v>141</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G65" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H65" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>75</v>
@@ -3806,7 +3803,7 @@
         <v>147</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>146</v>
@@ -3832,10 +3829,10 @@
         <v>142</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>76</v>
@@ -3849,22 +3846,22 @@
         <v>141</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G67" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>77</v>
@@ -3873,7 +3870,7 @@
         <v>147</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L67" s="4" t="s">
         <v>146</v>
@@ -3899,10 +3896,10 @@
         <v>142</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>10</v>
@@ -3916,22 +3913,22 @@
         <v>141</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G69" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H69" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>11</v>
@@ -3940,7 +3937,7 @@
         <v>147</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L69" s="4" t="s">
         <v>146</v>
@@ -3966,10 +3963,10 @@
         <v>142</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>78</v>
@@ -3983,22 +3980,22 @@
         <v>141</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G71" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="H71" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>79</v>
@@ -4007,7 +4004,7 @@
         <v>147</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>146</v>
@@ -4033,10 +4030,10 @@
         <v>142</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>80</v>
@@ -4050,22 +4047,22 @@
         <v>141</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>81</v>
@@ -4074,7 +4071,7 @@
         <v>147</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>146</v>
@@ -4100,16 +4097,16 @@
         <v>142</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -4117,22 +4114,22 @@
         <v>141</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>83</v>
@@ -4141,7 +4138,7 @@
         <v>147</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>146</v>
@@ -4167,10 +4164,10 @@
         <v>142</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>84</v>
@@ -4184,22 +4181,22 @@
         <v>141</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G77" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>85</v>
@@ -4208,7 +4205,7 @@
         <v>147</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>146</v>
@@ -4234,16 +4231,16 @@
         <v>142</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -4251,22 +4248,22 @@
         <v>141</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>87</v>
@@ -4275,7 +4272,7 @@
         <v>147</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>146</v>
@@ -4301,16 +4298,16 @@
         <v>142</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -4318,22 +4315,22 @@
         <v>141</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G81" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H81" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>13</v>
@@ -4368,16 +4365,16 @@
         <v>142</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -4385,22 +4382,22 @@
         <v>141</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G83" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>89</v>
@@ -4435,16 +4432,16 @@
         <v>142</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -4452,22 +4449,22 @@
         <v>141</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G85" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>15</v>
@@ -4502,16 +4499,16 @@
         <v>142</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4519,22 +4516,22 @@
         <v>141</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G87" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>91</v>
@@ -4569,16 +4566,16 @@
         <v>142</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -4586,22 +4583,22 @@
         <v>141</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G89" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>93</v>
@@ -4624,7 +4621,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P89" s="4" t="str">
         <f>D89 &amp; E89 &amp; "_" &amp; F89</f>
@@ -4639,10 +4636,10 @@
         <v>142</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>94</v>
@@ -4656,22 +4653,22 @@
         <v>141</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>95</v>
@@ -4694,7 +4691,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P91" s="4" t="str">
         <f>D91 &amp; E91 &amp; "_" &amp; F91</f>
@@ -4709,16 +4706,16 @@
         <v>142</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -4726,22 +4723,22 @@
         <v>141</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G93" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="I93" s="5" t="s">
         <v>97</v>
@@ -4764,7 +4761,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P93" s="5" t="str">
         <f>D93 &amp; E93 &amp; "_" &amp; F93</f>
@@ -4780,10 +4777,10 @@
         <v>142</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>98</v>
@@ -4797,22 +4794,22 @@
         <v>141</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G95" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>99</v>
@@ -4835,7 +4832,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O95" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P95" s="5" t="str">
         <f>D95 &amp; E95 &amp; "_" &amp; F95</f>
@@ -4851,16 +4848,16 @@
         <v>142</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -4868,22 +4865,22 @@
         <v>141</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G97" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H97" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>17</v>
@@ -4918,16 +4915,16 @@
         <v>142</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -4935,22 +4932,22 @@
         <v>141</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G99" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>101</v>
@@ -4985,16 +4982,16 @@
         <v>142</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -5002,22 +4999,22 @@
         <v>141</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G101" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>103</v>
@@ -5040,7 +5037,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P101" s="4" t="str">
         <f>D101 &amp; E101 &amp; "_" &amp; F101</f>
@@ -5055,10 +5052,10 @@
         <v>142</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>104</v>
@@ -5072,22 +5069,22 @@
         <v>141</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G103" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H103" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>105</v>
@@ -5110,7 +5107,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P103" s="4" t="str">
         <f>D103 &amp; E103 &amp; "_" &amp; F103</f>
@@ -5125,16 +5122,16 @@
         <v>142</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -5142,22 +5139,22 @@
         <v>141</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G105" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H105" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="I105" s="5" t="s">
         <v>107</v>
@@ -5188,10 +5185,10 @@
         <v>142</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>18</v>
@@ -5205,22 +5202,22 @@
         <v>141</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5255,10 +5252,10 @@
         <v>142</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>108</v>
@@ -5272,22 +5269,22 @@
         <v>141</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G109" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H109" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>109</v>
@@ -5322,10 +5319,10 @@
         <v>142</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>110</v>
@@ -5339,22 +5336,22 @@
         <v>141</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G111" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>111</v>
@@ -5389,16 +5386,16 @@
         <v>142</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -5406,22 +5403,22 @@
         <v>141</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G113" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>113</v>
@@ -5456,10 +5453,10 @@
         <v>142</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>20</v>
@@ -5473,22 +5470,22 @@
         <v>141</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G115" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>21</v>
@@ -5523,10 +5520,10 @@
         <v>142</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>114</v>
@@ -5540,22 +5537,22 @@
         <v>141</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G117" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>115</v>
@@ -5590,16 +5587,16 @@
         <v>142</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -5607,22 +5604,22 @@
         <v>141</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G119" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>117</v>
@@ -5645,7 +5642,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P119" s="4" t="str">
         <f>D119 &amp; E119 &amp; "_" &amp; F119</f>
@@ -5660,10 +5657,10 @@
         <v>142</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>118</v>
@@ -5677,22 +5674,22 @@
         <v>141</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G121" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>119</v>
@@ -5715,7 +5712,7 @@
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P121" s="4" t="str">
         <f>D121 &amp; E121 &amp; "_" &amp; F121</f>
@@ -5730,10 +5727,10 @@
         <v>142</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I122" s="4" t="s">
         <v>120</v>
@@ -5747,22 +5744,22 @@
         <v>141</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G123" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>121</v>
@@ -5781,7 +5778,7 @@
         <v>groupWeaponsT3_TBD</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O123" s="6"/>
       <c r="P123" s="4" t="str">
@@ -5797,10 +5794,10 @@
         <v>142</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>122</v>
@@ -5814,28 +5811,28 @@
         <v>141</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G125" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>123</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L125" s="4" t="s">
         <v>143</v>
@@ -5861,10 +5858,10 @@
         <v>142</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>124</v>
@@ -5878,28 +5875,28 @@
         <v>141</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G127" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>125</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>143</v>
@@ -5925,10 +5922,10 @@
         <v>142</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>126</v>
@@ -5942,28 +5939,28 @@
         <v>141</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>127</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L129" s="4" t="s">
         <v>143</v>
@@ -5989,7 +5986,7 @@
         <v>142</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>128</v>
@@ -6003,22 +6000,22 @@
         <v>141</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G131" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="H131" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="I131" s="4" t="s">
         <v>129</v>
@@ -6027,7 +6024,7 @@
         <v>147</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L131" s="4" t="s">
         <v>146</v>
@@ -6053,7 +6050,7 @@
         <v>142</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>130</v>
@@ -6067,22 +6064,22 @@
         <v>141</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G133" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>131</v>
@@ -6101,7 +6098,7 @@
         <v>groupWeaponsT5_Boomstick</v>
       </c>
       <c r="N133" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O133" s="6"/>
       <c r="P133" s="4" t="str">
@@ -6117,16 +6114,16 @@
         <v>142</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -6134,22 +6131,22 @@
         <v>141</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G135" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>133</v>
@@ -6168,7 +6165,7 @@
         <v>groupWeaponsT4_Archery</v>
       </c>
       <c r="N135" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O135" s="6"/>
       <c r="P135" s="4" t="str">
@@ -6184,7 +6181,7 @@
         <v>142</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>134</v>
@@ -6198,22 +6195,22 @@
         <v>141</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G137" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H137" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>135</v>
@@ -6222,7 +6219,7 @@
         <v>166</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L137" s="4" t="s">
         <v>143</v>
@@ -6248,16 +6245,16 @@
         <v>142</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -6265,22 +6262,22 @@
         <v>141</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G139" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H139" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>157</v>
@@ -6299,7 +6296,7 @@
         <v>groupWeaponsT4_Deep Cuts</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P139" s="4" t="str">
         <f>D139 &amp; E139 &amp; "_" &amp; F139</f>
@@ -6314,16 +6311,16 @@
         <v>142</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -6331,22 +6328,22 @@
         <v>141</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G141" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H141" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>159</v>
@@ -6365,7 +6362,7 @@
         <v>groupWeaponsT4_Skull Crusher</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P141" s="4" t="str">
         <f>D141 &amp; E141 &amp; "_" &amp; F141</f>
@@ -6380,16 +6377,16 @@
         <v>142</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -6397,22 +6394,22 @@
         <v>141</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G143" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="H143" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>161</v>
@@ -6431,7 +6428,7 @@
         <v>groupWeaponsT4_Spear Master</v>
       </c>
       <c r="N143" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P143" s="4" t="str">
         <f>D143 &amp; E143 &amp; "_" &amp; F143</f>
@@ -6445,9 +6442,9 @@
         <filter val="yes"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="2">
+    <filterColumn colId="10">
       <filters>
-        <filter val="T4"/>
+        <filter val="Gunslinger"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A4ADB-477E-4CC3-B925-CC5F40B2CAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555134A-5255-401F-B52F-3DFA8A22A04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$B$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="390">
   <si>
     <t>IZYgunT1ARCabineM608SurvivalRifle,items,gun,,,Model 608 Survival Rifle (T1),,,,,,,,,,,,,</t>
   </si>
@@ -1111,6 +1113,93 @@
   </si>
   <si>
     <t>revolver</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo25mmGrenadeFRAGS' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo25mmGrenadeHE' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo25mmGrenadeTraining' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo45ACPArmorpiecing' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo45ACPBulletBall' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo45ACPEnhanced' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo45ACPHighpower' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmArmorPiercing' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmArmorPiercingBundle' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmBulletBall' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmBulletBallBundle' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmHIpower' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammo556mmHIpowerBundle' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoBundle45ACPArmorpiecing' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoBundle45ACPBulletBall' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoBundle45ACPEnhanced' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoBundle45ACPHighpower' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoCrossbowLightBoltIron' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoCrossbowLightBoltSteelAP' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoCrossbowLightBoltStone' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoleadball' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoMuzzleloaderscattershot' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoMuzzleloadershot' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoRocketRPGHE' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoRocketRPGIncendiary' or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoRocketRPGTraning' or </t>
+  </si>
+  <si>
+    <t>@name='ammoShotgunShellPremium'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@name='ammoShotgunShellPremium' or </t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1225,6 +1314,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6458,4 +6553,348 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE20945E-AFE4-4A39-959D-59DB8ED64220}">
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="11"/>
+    <col min="2" max="2" width="47.33203125" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="11">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="11">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B44" xr:uid="{DE20945E-AFE4-4A39-959D-59DB8ED64220}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555134A-5255-401F-B52F-3DFA8A22A04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38C430D-16BF-48C7-A337-68E7E9A0E8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6545,7 +6545,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
-    <filterColumn colId="6">
+    <filterColumn colId="10">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38C430D-16BF-48C7-A337-68E7E9A0E8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADA6C80-D85C-4974-895E-5D1188730E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -1800,7 +1800,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6546,9 +6546,9 @@
   </sheetData>
   <autoFilter ref="A1:Q143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
     <filterColumn colId="10">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
+      <filters>
+        <filter val="DeadEye"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADA6C80-D85C-4974-895E-5D1188730E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D165FC-2B54-4E96-AFF5-C2B5B2F3A8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$B$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="391">
   <si>
     <t>IZYgunT1ARCabineM608SurvivalRifle,items,gun,,,Model 608 Survival Rifle (T1),,,,,,,,,,,,,</t>
   </si>
@@ -1200,13 +1200,16 @@
   </si>
   <si>
     <t xml:space="preserve">@name='ammoShotgunShellPremium' or </t>
+  </si>
+  <si>
+    <t>LOCAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1231,8 +1234,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1248,18 +1266,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1297,7 +1303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1308,23 +1314,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1634,8 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q143"/>
+  <dimension ref="A1:R143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="7.109375" style="3" customWidth="1"/>
@@ -1644,20 +1665,21 @@
     <col min="5" max="5" width="5" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="41.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="3" customWidth="1"/>
-    <col min="14" max="15" width="32.44140625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="23.5546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="32.88671875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="39.6640625" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="3"/>
+    <col min="8" max="8" width="41.33203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="3" customWidth="1"/>
+    <col min="15" max="16" width="32.44140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="23.5546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="32.88671875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="39.6640625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>136</v>
       </c>
@@ -1679,38 +1701,41 @@
       <c r="G1" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1720,14 +1745,17 @@
       <c r="C2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1749,38 +1777,41 @@
       <c r="G3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="3" t="str">
-        <f>"groupWeapons" &amp; C3 &amp; "_" &amp; K3</f>
+      <c r="N3" s="3" t="str">
+        <f>"groupWeapons" &amp; C3 &amp; "_" &amp; L3</f>
         <v>groupWeaponsT0_DeadEye</v>
       </c>
-      <c r="N3" s="3" t="str">
-        <f>D3 &amp; E3 &amp; "_" &amp; K3</f>
+      <c r="O3" s="3" t="str">
+        <f>D3 &amp; E3 &amp; "_" &amp; L3</f>
         <v>groupWeaponsT0_DeadEye</v>
       </c>
-      <c r="P3" s="3" t="str">
+      <c r="Q3" s="3" t="str">
         <f>D3 &amp; E3 &amp; "_" &amp; F3</f>
         <v>groupWeaponsT0_Ranged</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1790,17 +1821,20 @@
       <c r="C4" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1819,41 +1853,44 @@
       <c r="F5" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M5" s="3" t="str">
-        <f>"groupWeapons" &amp; C5 &amp; "_" &amp; K5</f>
+      <c r="N5" s="3" t="str">
+        <f>"groupWeapons" &amp; C5 &amp; "_" &amp; L5</f>
         <v>groupWeaponsT1_Machinegunner</v>
       </c>
-      <c r="N5" s="3" t="str">
-        <f>D5 &amp; E5 &amp; "_" &amp; K5</f>
+      <c r="O5" s="3" t="str">
+        <f>D5 &amp; E5 &amp; "_" &amp; L5</f>
         <v>groupWeaponsT1_Machinegunner</v>
       </c>
-      <c r="P5" s="3" t="str">
+      <c r="Q5" s="3" t="str">
         <f>D5 &amp; E5 &amp; "_" &amp; F5</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1863,17 +1900,20 @@
       <c r="C6" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1892,41 +1932,44 @@
       <c r="F7" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="3" t="str">
-        <f>"groupWeapons" &amp; C7 &amp; "_" &amp; K7</f>
+      <c r="N7" s="3" t="str">
+        <f>"groupWeapons" &amp; C7 &amp; "_" &amp; L7</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="N7" s="3" t="str">
-        <f>D7 &amp; E7 &amp; "_" &amp; K7</f>
+      <c r="O7" s="3" t="str">
+        <f>D7 &amp; E7 &amp; "_" &amp; L7</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="P7" s="3" t="str">
+      <c r="Q7" s="3" t="str">
         <f>D7 &amp; E7 &amp; "_" &amp; F7</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1936,17 +1979,20 @@
       <c r="C8" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1965,41 +2011,44 @@
       <c r="F9" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M9" s="3" t="str">
-        <f>"groupWeapons" &amp; C9 &amp; "_" &amp; K9</f>
+      <c r="N9" s="3" t="str">
+        <f>"groupWeapons" &amp; C9 &amp; "_" &amp; L9</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="N9" s="3" t="str">
-        <f>D9 &amp; E9 &amp; "_" &amp; K9</f>
+      <c r="O9" s="3" t="str">
+        <f>D9 &amp; E9 &amp; "_" &amp; L9</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P9" s="3" t="str">
+      <c r="Q9" s="3" t="str">
         <f>D9 &amp; E9 &amp; "_" &amp; F9</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2009,17 +2058,20 @@
       <c r="C10" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2038,41 +2090,44 @@
       <c r="F11" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M11" s="3" t="str">
-        <f>"groupWeapons" &amp; C11 &amp; "_" &amp; K11</f>
+      <c r="N11" s="3" t="str">
+        <f>"groupWeapons" &amp; C11 &amp; "_" &amp; L11</f>
         <v>groupWeaponsT4_Machinegunner</v>
       </c>
-      <c r="N11" s="3" t="str">
-        <f>D11 &amp; E11 &amp; "_" &amp; K11</f>
+      <c r="O11" s="3" t="str">
+        <f>D11 &amp; E11 &amp; "_" &amp; L11</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P11" s="3" t="str">
+      <c r="Q11" s="3" t="str">
         <f>D11 &amp; E11 &amp; "_" &amp; F11</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2082,17 +2137,20 @@
       <c r="C12" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2111,41 +2169,44 @@
       <c r="F13" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M13" s="3" t="str">
-        <f>"groupWeapons" &amp; C13 &amp; "_" &amp; K13</f>
+      <c r="N13" s="3" t="str">
+        <f>"groupWeapons" &amp; C13 &amp; "_" &amp; L13</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="N13" s="3" t="str">
-        <f>D13 &amp; E13 &amp; "_" &amp; K13</f>
+      <c r="O13" s="3" t="str">
+        <f>D13 &amp; E13 &amp; "_" &amp; L13</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="P13" s="3" t="str">
+      <c r="Q13" s="3" t="str">
         <f>D13 &amp; E13 &amp; "_" &amp; F13</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2155,17 +2216,20 @@
       <c r="C14" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2184,41 +2248,44 @@
       <c r="F15" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M15" s="3" t="str">
-        <f>"groupWeapons" &amp; C15 &amp; "_" &amp; K15</f>
+      <c r="N15" s="3" t="str">
+        <f>"groupWeapons" &amp; C15 &amp; "_" &amp; L15</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="N15" s="3" t="str">
-        <f>D15 &amp; E15 &amp; "_" &amp; K15</f>
+      <c r="O15" s="3" t="str">
+        <f>D15 &amp; E15 &amp; "_" &amp; L15</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P15" s="3" t="str">
+      <c r="Q15" s="3" t="str">
         <f>D15 &amp; E15 &amp; "_" &amp; F15</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2228,17 +2295,20 @@
       <c r="C16" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2260,38 +2330,41 @@
       <c r="G17" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="L17" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="3" t="str">
-        <f>"groupWeapons" &amp; C17 &amp; "_" &amp; K17</f>
+      <c r="N17" s="3" t="str">
+        <f>"groupWeapons" &amp; C17 &amp; "_" &amp; L17</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="N17" s="3" t="str">
-        <f>D17 &amp; E17 &amp; "_" &amp; K17</f>
+      <c r="O17" s="3" t="str">
+        <f>D17 &amp; E17 &amp; "_" &amp; L17</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P17" s="3" t="str">
+      <c r="Q17" s="3" t="str">
         <f>D17 &amp; E17 &amp; "_" &amp; F17</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2301,17 +2374,20 @@
       <c r="C18" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2330,41 +2406,44 @@
       <c r="F19" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M19" s="3" t="str">
-        <f>"groupWeapons" &amp; C19 &amp; "_" &amp; K19</f>
+      <c r="N19" s="3" t="str">
+        <f>"groupWeapons" &amp; C19 &amp; "_" &amp; L19</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="N19" s="3" t="str">
-        <f>D19 &amp; E19 &amp; "_" &amp; K19</f>
+      <c r="O19" s="3" t="str">
+        <f>D19 &amp; E19 &amp; "_" &amp; L19</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P19" s="3" t="str">
+      <c r="Q19" s="3" t="str">
         <f>D19 &amp; E19 &amp; "_" &amp; F19</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2374,17 +2453,20 @@
       <c r="C20" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2403,38 +2485,41 @@
       <c r="F21" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M21" s="3" t="str">
-        <f>"groupWeapons" &amp; C21 &amp; "_" &amp; K21</f>
+      <c r="N21" s="3" t="str">
+        <f>"groupWeapons" &amp; C21 &amp; "_" &amp; L21</f>
         <v>groupWeaponsT4_Machinegunner</v>
       </c>
-      <c r="N21" s="3" t="str">
-        <f>D21 &amp; E21 &amp; "_" &amp; K21</f>
+      <c r="O21" s="3" t="str">
+        <f>D21 &amp; E21 &amp; "_" &amp; L21</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P21" s="3" t="str">
+      <c r="Q21" s="3" t="str">
         <f>D21 &amp; E21 &amp; "_" &amp; F21</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -2444,14 +2529,17 @@
       <c r="C22" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2473,35 +2561,38 @@
       <c r="G23" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M23" s="3" t="str">
-        <f>"groupWeapons" &amp; C23 &amp; "_" &amp; K23</f>
+      <c r="N23" s="3" t="str">
+        <f>"groupWeapons" &amp; C23 &amp; "_" &amp; L23</f>
         <v>groupWeaponsT0_Gunslinger</v>
       </c>
-      <c r="N23" s="3" t="str">
-        <f>D23 &amp; E23 &amp; "_" &amp; K23</f>
+      <c r="O23" s="3" t="str">
+        <f>D23 &amp; E23 &amp; "_" &amp; L23</f>
         <v>groupWeaponsT0_Gunslinger</v>
       </c>
-      <c r="P23" s="3" t="str">
+      <c r="Q23" s="3" t="str">
         <f>D23 &amp; E23 &amp; "_" &amp; F23</f>
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -2511,14 +2602,17 @@
       <c r="C24" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2540,38 +2634,41 @@
       <c r="G25" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M25" s="3" t="str">
-        <f>"groupWeapons" &amp; C25 &amp; "_" &amp; K25</f>
+      <c r="N25" s="3" t="str">
+        <f>"groupWeapons" &amp; C25 &amp; "_" &amp; L25</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N25" s="3" t="str">
-        <f>D25 &amp; E25 &amp; "_" &amp; K25</f>
+      <c r="O25" s="3" t="str">
+        <f>D25 &amp; E25 &amp; "_" &amp; L25</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="O25" s="3" t="s">
+      <c r="P25" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="P25" s="3" t="str">
+      <c r="Q25" s="3" t="str">
         <f>D25 &amp; E25 &amp; "_" &amp; F25</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -2581,14 +2678,17 @@
       <c r="C26" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2610,35 +2710,38 @@
       <c r="G27" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M27" s="3" t="str">
-        <f>"groupWeapons" &amp; C27 &amp; "_" &amp; K27</f>
+      <c r="N27" s="3" t="str">
+        <f>"groupWeapons" &amp; C27 &amp; "_" &amp; L27</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N27" s="3" t="str">
-        <f>D27 &amp; E27 &amp; "_" &amp; K27</f>
+      <c r="O27" s="3" t="str">
+        <f>D27 &amp; E27 &amp; "_" &amp; L27</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="P27" s="3" t="str">
+      <c r="Q27" s="3" t="str">
         <f>D27 &amp; E27 &amp; "_" &amp; F27</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -2648,14 +2751,17 @@
       <c r="C28" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2677,35 +2783,38 @@
       <c r="G29" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M29" s="3" t="str">
-        <f>"groupWeapons" &amp; C29 &amp; "_" &amp; K29</f>
+      <c r="N29" s="3" t="str">
+        <f>"groupWeapons" &amp; C29 &amp; "_" &amp; L29</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="N29" s="3" t="str">
-        <f>D29 &amp; E29 &amp; "_" &amp; K29</f>
+      <c r="O29" s="3" t="str">
+        <f>D29 &amp; E29 &amp; "_" &amp; L29</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="P29" s="3" t="str">
+      <c r="Q29" s="3" t="str">
         <f>D29 &amp; E29 &amp; "_" &amp; F29</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -2715,14 +2824,17 @@
       <c r="C30" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -2744,38 +2856,41 @@
       <c r="G31" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="K31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="M31" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M31" s="3" t="str">
-        <f>"groupWeapons" &amp; C31 &amp; "_" &amp; K31</f>
+      <c r="N31" s="3" t="str">
+        <f>"groupWeapons" &amp; C31 &amp; "_" &amp; L31</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N31" s="3" t="str">
-        <f>D31 &amp; E31 &amp; "_" &amp; K31</f>
+      <c r="O31" s="3" t="str">
+        <f>D31 &amp; E31 &amp; "_" &amp; L31</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O31" s="3" t="s">
+      <c r="P31" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="P31" s="3" t="str">
+      <c r="Q31" s="3" t="str">
         <f>D31 &amp; E31 &amp; "_" &amp; F31</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -2785,14 +2900,17 @@
       <c r="C32" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2814,38 +2932,41 @@
       <c r="G33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="M33" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M33" s="3" t="str">
-        <f>"groupWeapons" &amp; C33 &amp; "_" &amp; K33</f>
+      <c r="N33" s="3" t="str">
+        <f>"groupWeapons" &amp; C33 &amp; "_" &amp; L33</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N33" s="3" t="str">
-        <f>D33 &amp; E33 &amp; "_" &amp; K33</f>
+      <c r="O33" s="3" t="str">
+        <f>D33 &amp; E33 &amp; "_" &amp; L33</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O33" s="3" t="s">
+      <c r="P33" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="P33" s="3" t="str">
+      <c r="Q33" s="3" t="str">
         <f>D33 &amp; E33 &amp; "_" &amp; F33</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2855,14 +2976,17 @@
       <c r="C34" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -2884,35 +3008,38 @@
       <c r="G35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M35" s="3" t="str">
-        <f>"groupWeapons" &amp; C35 &amp; "_" &amp; K35</f>
+      <c r="N35" s="3" t="str">
+        <f>"groupWeapons" &amp; C35 &amp; "_" &amp; L35</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="N35" s="3" t="str">
-        <f>D35 &amp; E35 &amp; "_" &amp; K35</f>
+      <c r="O35" s="3" t="str">
+        <f>D35 &amp; E35 &amp; "_" &amp; L35</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="P35" s="3" t="str">
+      <c r="Q35" s="3" t="str">
         <f>D35 &amp; E35 &amp; "_" &amp; F35</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -2922,14 +3049,17 @@
       <c r="C36" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="J36" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2951,35 +3081,38 @@
       <c r="G37" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M37" s="3" t="str">
-        <f>"groupWeapons" &amp; C37 &amp; "_" &amp; K37</f>
+      <c r="N37" s="3" t="str">
+        <f>"groupWeapons" &amp; C37 &amp; "_" &amp; L37</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="N37" s="3" t="str">
-        <f>D37 &amp; E37 &amp; "_" &amp; K37</f>
+      <c r="O37" s="3" t="str">
+        <f>D37 &amp; E37 &amp; "_" &amp; L37</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="P37" s="3" t="str">
+      <c r="Q37" s="3" t="str">
         <f>D37 &amp; E37 &amp; "_" &amp; F37</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2989,14 +3122,17 @@
       <c r="C38" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3018,38 +3154,41 @@
       <c r="G39" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="J39" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="L39" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M39" s="3" t="str">
-        <f>"groupWeapons" &amp; C39 &amp; "_" &amp; K39</f>
+      <c r="N39" s="3" t="str">
+        <f>"groupWeapons" &amp; C39 &amp; "_" &amp; L39</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N39" s="3" t="str">
-        <f>D39 &amp; E39 &amp; "_" &amp; K39</f>
+      <c r="O39" s="3" t="str">
+        <f>D39 &amp; E39 &amp; "_" &amp; L39</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O39" s="3" t="s">
+      <c r="P39" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P39" s="3" t="str">
+      <c r="Q39" s="3" t="str">
         <f>D39 &amp; E39 &amp; "_" &amp; F39</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3059,14 +3198,17 @@
       <c r="C40" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3088,38 +3230,41 @@
       <c r="G41" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M41" s="3" t="str">
-        <f>"groupWeapons" &amp; C41 &amp; "_" &amp; K41</f>
+      <c r="N41" s="3" t="str">
+        <f>"groupWeapons" &amp; C41 &amp; "_" &amp; L41</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N41" s="3" t="str">
-        <f>D41 &amp; E41 &amp; "_" &amp; K41</f>
+      <c r="O41" s="3" t="str">
+        <f>D41 &amp; E41 &amp; "_" &amp; L41</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O41" s="3" t="s">
+      <c r="P41" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P41" s="3" t="str">
+      <c r="Q41" s="3" t="str">
         <f>D41 &amp; E41 &amp; "_" &amp; F41</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3129,14 +3274,17 @@
       <c r="C42" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3158,35 +3306,35 @@
       <c r="G43" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="I43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="M43" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M43" s="3" t="str">
-        <f>"groupWeapons" &amp; C43 &amp; "_" &amp; K43</f>
+      <c r="N43" s="3" t="str">
+        <f>"groupWeapons" &amp; C43 &amp; "_" &amp; L43</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N43" s="3" t="str">
-        <f>D43 &amp; E43 &amp; "_" &amp; K43</f>
+      <c r="O43" s="3" t="str">
+        <f>D43 &amp; E43 &amp; "_" &amp; L43</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="P43" s="3" t="str">
+      <c r="Q43" s="3" t="str">
         <f>D43 &amp; E43 &amp; "_" &amp; F43</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3196,14 +3344,17 @@
       <c r="C44" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3225,38 +3376,41 @@
       <c r="G45" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M45" s="3" t="str">
-        <f>"groupWeapons" &amp; C45 &amp; "_" &amp; K45</f>
+      <c r="N45" s="3" t="str">
+        <f>"groupWeapons" &amp; C45 &amp; "_" &amp; L45</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N45" s="3" t="str">
-        <f>D45 &amp; E45 &amp; "_" &amp; K45</f>
+      <c r="O45" s="3" t="str">
+        <f>D45 &amp; E45 &amp; "_" &amp; L45</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P45" s="3" t="str">
+      <c r="Q45" s="3" t="str">
         <f>D45 &amp; E45 &amp; "_" &amp; F45</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3266,14 +3420,17 @@
       <c r="C46" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="J46" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3295,35 +3452,38 @@
       <c r="G47" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K47" s="9" t="s">
+      <c r="L47" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M47" s="3" t="str">
-        <f>"groupWeapons" &amp; C47 &amp; "_" &amp; K47</f>
+      <c r="N47" s="3" t="str">
+        <f>"groupWeapons" &amp; C47 &amp; "_" &amp; L47</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="N47" s="3" t="str">
-        <f>D47 &amp; E47 &amp; "_" &amp; K47</f>
+      <c r="O47" s="3" t="str">
+        <f>D47 &amp; E47 &amp; "_" &amp; L47</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P47" s="3" t="str">
+      <c r="Q47" s="3" t="str">
         <f>D47 &amp; E47 &amp; "_" &amp; F47</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -3333,14 +3493,17 @@
       <c r="C48" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3362,35 +3525,38 @@
       <c r="G49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K49" s="9" t="s">
+      <c r="L49" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M49" s="3" t="str">
-        <f>"groupWeapons" &amp; C49 &amp; "_" &amp; K49</f>
+      <c r="N49" s="3" t="str">
+        <f>"groupWeapons" &amp; C49 &amp; "_" &amp; L49</f>
         <v>groupWeaponsT4_DeadEye</v>
       </c>
-      <c r="N49" s="3" t="str">
-        <f>D49 &amp; E49 &amp; "_" &amp; K49</f>
+      <c r="O49" s="3" t="str">
+        <f>D49 &amp; E49 &amp; "_" &amp; L49</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P49" s="3" t="str">
+      <c r="Q49" s="3" t="str">
         <f>D49 &amp; E49 &amp; "_" &amp; F49</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3400,14 +3566,17 @@
       <c r="C50" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="J50" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3429,35 +3598,38 @@
       <c r="G51" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K51" s="9" t="s">
+      <c r="L51" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L51" s="3" t="s">
+      <c r="M51" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M51" s="3" t="str">
-        <f>"groupWeapons" &amp; C51 &amp; "_" &amp; K51</f>
+      <c r="N51" s="3" t="str">
+        <f>"groupWeapons" &amp; C51 &amp; "_" &amp; L51</f>
         <v>groupWeaponsT1_DeadEye</v>
       </c>
-      <c r="N51" s="3" t="str">
-        <f>D51 &amp; E51 &amp; "_" &amp; K51</f>
+      <c r="O51" s="3" t="str">
+        <f>D51 &amp; E51 &amp; "_" &amp; L51</f>
         <v>groupWeaponsT1_DeadEye</v>
       </c>
-      <c r="P51" s="3" t="str">
+      <c r="Q51" s="3" t="str">
         <f>D51 &amp; E51 &amp; "_" &amp; F51</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3467,14 +3639,17 @@
       <c r="C52" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3496,35 +3671,38 @@
       <c r="G53" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K53" s="9" t="s">
+      <c r="L53" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M53" s="3" t="str">
-        <f>"groupWeapons" &amp; C53 &amp; "_" &amp; K53</f>
+      <c r="N53" s="3" t="str">
+        <f>"groupWeapons" &amp; C53 &amp; "_" &amp; L53</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="N53" s="3" t="str">
-        <f>D53 &amp; E53 &amp; "_" &amp; K53</f>
+      <c r="O53" s="3" t="str">
+        <f>D53 &amp; E53 &amp; "_" &amp; L53</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P53" s="3" t="str">
+      <c r="Q53" s="3" t="str">
         <f>D53 &amp; E53 &amp; "_" &amp; F53</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3534,14 +3712,17 @@
       <c r="C54" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3563,35 +3744,38 @@
       <c r="G55" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="J55" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K55" s="9" t="s">
+      <c r="L55" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L55" s="3" t="s">
+      <c r="M55" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M55" s="3" t="str">
-        <f>"groupWeapons" &amp; C55 &amp; "_" &amp; K55</f>
+      <c r="N55" s="3" t="str">
+        <f>"groupWeapons" &amp; C55 &amp; "_" &amp; L55</f>
         <v>groupWeaponsT4_DeadEye</v>
       </c>
-      <c r="N55" s="3" t="str">
-        <f>D55 &amp; E55 &amp; "_" &amp; K55</f>
+      <c r="O55" s="3" t="str">
+        <f>D55 &amp; E55 &amp; "_" &amp; L55</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P55" s="3" t="str">
+      <c r="Q55" s="3" t="str">
         <f>D55 &amp; E55 &amp; "_" &amp; F55</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3601,14 +3785,14 @@
       <c r="C56" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="I56" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="J56" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3630,35 +3814,38 @@
       <c r="G57" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H57" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="J57" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K57" s="9" t="s">
+      <c r="L57" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L57" s="3" t="s">
+      <c r="M57" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M57" s="3" t="str">
-        <f>"groupWeapons" &amp; C57 &amp; "_" &amp; K57</f>
+      <c r="N57" s="3" t="str">
+        <f>"groupWeapons" &amp; C57 &amp; "_" &amp; L57</f>
         <v>groupWeaponsT2_DeadEye</v>
       </c>
-      <c r="N57" s="3" t="str">
-        <f>D57 &amp; E57 &amp; "_" &amp; K57</f>
+      <c r="O57" s="3" t="str">
+        <f>D57 &amp; E57 &amp; "_" &amp; L57</f>
         <v>groupWeaponsT2_DeadEye</v>
       </c>
-      <c r="P57" s="3" t="str">
+      <c r="Q57" s="3" t="str">
         <f>D57 &amp; E57 &amp; "_" &amp; F57</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -3668,14 +3855,17 @@
       <c r="C58" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="J58" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3697,35 +3887,38 @@
       <c r="G59" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H59" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="J59" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K59" s="9" t="s">
+      <c r="L59" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M59" s="3" t="str">
-        <f>"groupWeapons" &amp; C59 &amp; "_" &amp; K59</f>
+      <c r="N59" s="3" t="str">
+        <f>"groupWeapons" &amp; C59 &amp; "_" &amp; L59</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="N59" s="3" t="str">
-        <f>D59 &amp; E59 &amp; "_" &amp; K59</f>
+      <c r="O59" s="3" t="str">
+        <f>D59 &amp; E59 &amp; "_" &amp; L59</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P59" s="3" t="str">
+      <c r="Q59" s="3" t="str">
         <f>D59 &amp; E59 &amp; "_" &amp; F59</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3735,14 +3928,17 @@
       <c r="C60" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="J60" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3764,35 +3960,38 @@
       <c r="G61" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H61" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="J61" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K61" s="9" t="s">
+      <c r="L61" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L61" s="3" t="s">
+      <c r="M61" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M61" s="3" t="str">
-        <f>"groupWeapons" &amp; C61 &amp; "_" &amp; K61</f>
+      <c r="N61" s="3" t="str">
+        <f>"groupWeapons" &amp; C61 &amp; "_" &amp; L61</f>
         <v>groupWeaponsT4_DeadEye</v>
       </c>
-      <c r="N61" s="3" t="str">
-        <f>D61 &amp; E61 &amp; "_" &amp; K61</f>
+      <c r="O61" s="3" t="str">
+        <f>D61 &amp; E61 &amp; "_" &amp; L61</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P61" s="3" t="str">
+      <c r="Q61" s="3" t="str">
         <f>D61 &amp; E61 &amp; "_" &amp; F61</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -3802,14 +4001,17 @@
       <c r="C62" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="J62" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -3831,35 +4033,35 @@
       <c r="G63" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="I63" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="J63" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K63" s="9" t="s">
+      <c r="L63" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L63" s="3" t="s">
+      <c r="M63" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M63" s="3" t="str">
-        <f>"groupWeapons" &amp; C63 &amp; "_" &amp; K63</f>
+      <c r="N63" s="3" t="str">
+        <f>"groupWeapons" &amp; C63 &amp; "_" &amp; L63</f>
         <v>groupWeaponsT4_DeadEye</v>
       </c>
-      <c r="N63" s="3" t="str">
-        <f>D63 &amp; E63 &amp; "_" &amp; K63</f>
+      <c r="O63" s="3" t="str">
+        <f>D63 &amp; E63 &amp; "_" &amp; L63</f>
         <v>groupWeaponsT3_DeadEye</v>
       </c>
-      <c r="P63" s="3" t="str">
+      <c r="Q63" s="3" t="str">
         <f>D63 &amp; E63 &amp; "_" &amp; F63</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3869,14 +4071,17 @@
       <c r="C64" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H64" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="J64" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -3898,35 +4103,38 @@
       <c r="G65" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="J65" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K65" s="9" t="s">
+      <c r="L65" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="M65" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M65" s="3" t="str">
-        <f>"groupWeapons" &amp; C65 &amp; "_" &amp; K65</f>
+      <c r="N65" s="3" t="str">
+        <f>"groupWeapons" &amp; C65 &amp; "_" &amp; L65</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="N65" s="3" t="str">
-        <f>D65 &amp; E65 &amp; "_" &amp; K65</f>
+      <c r="O65" s="3" t="str">
+        <f>D65 &amp; E65 &amp; "_" &amp; L65</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="P65" s="3" t="str">
+      <c r="Q65" s="3" t="str">
         <f>D65 &amp; E65 &amp; "_" &amp; F65</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -3936,14 +4144,17 @@
       <c r="C66" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H66" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="J66" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3965,35 +4176,38 @@
       <c r="G67" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H67" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="J67" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K67" s="9" t="s">
+      <c r="L67" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L67" s="3" t="s">
+      <c r="M67" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M67" s="3" t="str">
-        <f>"groupWeapons" &amp; C67 &amp; "_" &amp; K67</f>
+      <c r="N67" s="3" t="str">
+        <f>"groupWeapons" &amp; C67 &amp; "_" &amp; L67</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="N67" s="3" t="str">
-        <f>D67 &amp; E67 &amp; "_" &amp; K67</f>
+      <c r="O67" s="3" t="str">
+        <f>D67 &amp; E67 &amp; "_" &amp; L67</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P67" s="3" t="str">
+      <c r="Q67" s="3" t="str">
         <f>D67 &amp; E67 &amp; "_" &amp; F67</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4003,14 +4217,17 @@
       <c r="C68" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H68" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="J68" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4032,35 +4249,38 @@
       <c r="G69" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="J69" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="K69" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K69" s="9" t="s">
+      <c r="L69" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L69" s="3" t="s">
+      <c r="M69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M69" s="3" t="str">
-        <f>"groupWeapons" &amp; C69 &amp; "_" &amp; K69</f>
+      <c r="N69" s="3" t="str">
+        <f>"groupWeapons" &amp; C69 &amp; "_" &amp; L69</f>
         <v>groupWeaponsT1_Machinegunner</v>
       </c>
-      <c r="N69" s="3" t="str">
-        <f>D69 &amp; E69 &amp; "_" &amp; K69</f>
+      <c r="O69" s="3" t="str">
+        <f>D69 &amp; E69 &amp; "_" &amp; L69</f>
         <v>groupWeaponsT1_Machinegunner</v>
       </c>
-      <c r="P69" s="3" t="str">
+      <c r="Q69" s="3" t="str">
         <f>D69 &amp; E69 &amp; "_" &amp; F69</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4070,14 +4290,17 @@
       <c r="C70" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="J70" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4099,35 +4322,38 @@
       <c r="G71" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="J71" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="K71" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K71" s="9" t="s">
+      <c r="L71" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="M71" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M71" s="3" t="str">
-        <f>"groupWeapons" &amp; C71 &amp; "_" &amp; K71</f>
+      <c r="N71" s="3" t="str">
+        <f>"groupWeapons" &amp; C71 &amp; "_" &amp; L71</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="N71" s="3" t="str">
-        <f>D71 &amp; E71 &amp; "_" &amp; K71</f>
+      <c r="O71" s="3" t="str">
+        <f>D71 &amp; E71 &amp; "_" &amp; L71</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="P71" s="3" t="str">
+      <c r="Q71" s="3" t="str">
         <f>D71 &amp; E71 &amp; "_" &amp; F71</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4137,14 +4363,17 @@
       <c r="C72" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4166,35 +4395,35 @@
       <c r="G73" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="J73" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="K73" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K73" s="9" t="s">
+      <c r="L73" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L73" s="3" t="s">
+      <c r="M73" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M73" s="3" t="str">
-        <f>"groupWeapons" &amp; C73 &amp; "_" &amp; K73</f>
+      <c r="N73" s="3" t="str">
+        <f>"groupWeapons" &amp; C73 &amp; "_" &amp; L73</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="N73" s="3" t="str">
-        <f>D73 &amp; E73 &amp; "_" &amp; K73</f>
+      <c r="O73" s="3" t="str">
+        <f>D73 &amp; E73 &amp; "_" &amp; L73</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P73" s="3" t="str">
+      <c r="Q73" s="3" t="str">
         <f>D73 &amp; E73 &amp; "_" &amp; F73</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4204,14 +4433,14 @@
       <c r="C74" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4233,35 +4462,35 @@
       <c r="G75" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="J75" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="K75" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K75" s="9" t="s">
+      <c r="L75" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="M75" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M75" s="3" t="str">
-        <f>"groupWeapons" &amp; C75 &amp; "_" &amp; K75</f>
+      <c r="N75" s="3" t="str">
+        <f>"groupWeapons" &amp; C75 &amp; "_" &amp; L75</f>
         <v>groupWeaponsT4_Machinegunner</v>
       </c>
-      <c r="N75" s="3" t="str">
-        <f>D75 &amp; E75 &amp; "_" &amp; K75</f>
+      <c r="O75" s="3" t="str">
+        <f>D75 &amp; E75 &amp; "_" &amp; L75</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P75" s="3" t="str">
+      <c r="Q75" s="3" t="str">
         <f>D75 &amp; E75 &amp; "_" &amp; F75</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -4271,14 +4500,14 @@
       <c r="C76" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="J76" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -4300,35 +4529,35 @@
       <c r="G77" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="J77" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="K77" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="L77" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L77" s="3" t="s">
+      <c r="M77" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M77" s="3" t="str">
-        <f>"groupWeapons" &amp; C77 &amp; "_" &amp; K77</f>
+      <c r="N77" s="3" t="str">
+        <f>"groupWeapons" &amp; C77 &amp; "_" &amp; L77</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="N77" s="3" t="str">
-        <f>D77 &amp; E77 &amp; "_" &amp; K77</f>
+      <c r="O77" s="3" t="str">
+        <f>D77 &amp; E77 &amp; "_" &amp; L77</f>
         <v>groupWeaponsT2_Machinegunner</v>
       </c>
-      <c r="P77" s="3" t="str">
+      <c r="Q77" s="3" t="str">
         <f>D77 &amp; E77 &amp; "_" &amp; F77</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -4338,14 +4567,14 @@
       <c r="C78" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="J78" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -4367,35 +4596,35 @@
       <c r="G79" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="J79" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="K79" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K79" s="9" t="s">
+      <c r="L79" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="L79" s="3" t="s">
+      <c r="M79" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M79" s="3" t="str">
-        <f>"groupWeapons" &amp; C79 &amp; "_" &amp; K79</f>
+      <c r="N79" s="3" t="str">
+        <f>"groupWeapons" &amp; C79 &amp; "_" &amp; L79</f>
         <v>groupWeaponsT4_Machinegunner</v>
       </c>
-      <c r="N79" s="3" t="str">
-        <f>D79 &amp; E79 &amp; "_" &amp; K79</f>
+      <c r="O79" s="3" t="str">
+        <f>D79 &amp; E79 &amp; "_" &amp; L79</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P79" s="3" t="str">
+      <c r="Q79" s="3" t="str">
         <f>D79 &amp; E79 &amp; "_" &amp; F79</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -4405,14 +4634,14 @@
       <c r="C80" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="J80" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -4434,35 +4663,35 @@
       <c r="G81" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="J81" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L81" s="3" t="s">
+      <c r="M81" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M81" s="3" t="str">
-        <f>"groupWeapons" &amp; C81 &amp; "_" &amp; K81</f>
+      <c r="N81" s="3" t="str">
+        <f>"groupWeapons" &amp; C81 &amp; "_" &amp; L81</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N81" s="3" t="str">
-        <f>D81 &amp; E81 &amp; "_" &amp; K81</f>
+      <c r="O81" s="3" t="str">
+        <f>D81 &amp; E81 &amp; "_" &amp; L81</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="P81" s="3" t="str">
+      <c r="Q81" s="3" t="str">
         <f>D81 &amp; E81 &amp; "_" &amp; F81</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -4472,14 +4701,14 @@
       <c r="C82" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="I82" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="J82" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4501,35 +4730,35 @@
       <c r="G83" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="I83" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M83" s="3" t="str">
-        <f>"groupWeapons" &amp; C83 &amp; "_" &amp; K83</f>
+      <c r="N83" s="3" t="str">
+        <f>"groupWeapons" &amp; C83 &amp; "_" &amp; L83</f>
         <v>groupWeaponsT0_Gunslinger</v>
       </c>
-      <c r="N83" s="3" t="str">
-        <f>D83 &amp; E83 &amp; "_" &amp; K83</f>
+      <c r="O83" s="3" t="str">
+        <f>D83 &amp; E83 &amp; "_" &amp; L83</f>
         <v>groupWeaponsT0_Gunslinger</v>
       </c>
-      <c r="P83" s="3" t="str">
+      <c r="Q83" s="3" t="str">
         <f>D83 &amp; E83 &amp; "_" &amp; F83</f>
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -4539,14 +4768,14 @@
       <c r="C84" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="I84" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="J84" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4568,35 +4797,35 @@
       <c r="G85" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="I85" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="J85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="K85" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="L85" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L85" s="3" t="s">
+      <c r="M85" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M85" s="3" t="str">
-        <f>"groupWeapons" &amp; C85 &amp; "_" &amp; K85</f>
+      <c r="N85" s="3" t="str">
+        <f>"groupWeapons" &amp; C85 &amp; "_" &amp; L85</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N85" s="3" t="str">
-        <f>D85 &amp; E85 &amp; "_" &amp; K85</f>
+      <c r="O85" s="3" t="str">
+        <f>D85 &amp; E85 &amp; "_" &amp; L85</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="P85" s="3" t="str">
+      <c r="Q85" s="3" t="str">
         <f>D85 &amp; E85 &amp; "_" &amp; F85</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -4606,14 +4835,14 @@
       <c r="C86" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="I86" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="J86" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4635,35 +4864,35 @@
       <c r="G87" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="I87" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="J87" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="K87" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="L87" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="M87" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M87" s="3" t="str">
-        <f>"groupWeapons" &amp; C87 &amp; "_" &amp; K87</f>
+      <c r="N87" s="3" t="str">
+        <f>"groupWeapons" &amp; C87 &amp; "_" &amp; L87</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="N87" s="3" t="str">
-        <f>D87 &amp; E87 &amp; "_" &amp; K87</f>
+      <c r="O87" s="3" t="str">
+        <f>D87 &amp; E87 &amp; "_" &amp; L87</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="P87" s="3" t="str">
+      <c r="Q87" s="3" t="str">
         <f>D87 &amp; E87 &amp; "_" &amp; F87</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -4673,14 +4902,14 @@
       <c r="C88" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="I88" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="J88" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4702,38 +4931,38 @@
       <c r="G89" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M89" s="3" t="str">
-        <f>"groupWeapons" &amp; C89 &amp; "_" &amp; K89</f>
+      <c r="N89" s="3" t="str">
+        <f>"groupWeapons" &amp; C89 &amp; "_" &amp; L89</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N89" s="3" t="str">
-        <f>D89 &amp; E89 &amp; "_" &amp; K89</f>
+      <c r="O89" s="3" t="str">
+        <f>D89 &amp; E89 &amp; "_" &amp; L89</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O89" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P89" s="3" t="str">
+      <c r="Q89" s="3" t="str">
         <f>D89 &amp; E89 &amp; "_" &amp; F89</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4743,14 +4972,14 @@
       <c r="C90" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="I90" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="J90" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -4772,38 +5001,38 @@
       <c r="G91" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="I91" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="M91" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M91" s="3" t="str">
-        <f>"groupWeapons" &amp; C91 &amp; "_" &amp; K91</f>
+      <c r="N91" s="3" t="str">
+        <f>"groupWeapons" &amp; C91 &amp; "_" &amp; L91</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N91" s="3" t="str">
-        <f>D91 &amp; E91 &amp; "_" &amp; K91</f>
+      <c r="O91" s="3" t="str">
+        <f>D91 &amp; E91 &amp; "_" &amp; L91</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P91" s="3" t="str">
+      <c r="Q91" s="3" t="str">
         <f>D91 &amp; E91 &amp; "_" &amp; F91</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -4813,15 +5042,15 @@
       <c r="C92" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="I92" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="J92" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A93" s="13">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -4839,42 +5068,43 @@
       <c r="F93" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" s="12"/>
+      <c r="I93" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="I93" s="4" t="s">
+      <c r="J93" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J93" s="4" t="s">
+      <c r="K93" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="K93" s="4" t="s">
+      <c r="L93" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="L93" s="4" t="s">
+      <c r="M93" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="M93" s="4" t="str">
-        <f>"groupWeapons" &amp; C93 &amp; "_" &amp; K93</f>
+      <c r="N93" s="4" t="str">
+        <f>"groupWeapons" &amp; C93 &amp; "_" &amp; L93</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N93" s="4" t="str">
-        <f>D93 &amp; E93 &amp; "_" &amp; K93</f>
+      <c r="O93" s="4" t="str">
+        <f>D93 &amp; E93 &amp; "_" &amp; L93</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O93" s="4" t="s">
+      <c r="P93" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="P93" s="4" t="str">
+      <c r="Q93" s="4" t="str">
         <f>D93 &amp; E93 &amp; "_" &amp; F93</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q93" s="4"/>
-    </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R93" s="4"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -4884,15 +5114,15 @@
       <c r="C94" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A95" s="13">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -4910,42 +5140,43 @@
       <c r="F95" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H95" s="12"/>
+      <c r="I95" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I95" s="4" t="s">
+      <c r="J95" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J95" s="4" t="s">
+      <c r="K95" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="K95" s="4" t="s">
+      <c r="L95" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="L95" s="4" t="s">
+      <c r="M95" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="M95" s="4" t="str">
-        <f>"groupWeapons" &amp; C95 &amp; "_" &amp; K95</f>
+      <c r="N95" s="4" t="str">
+        <f>"groupWeapons" &amp; C95 &amp; "_" &amp; L95</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N95" s="4" t="str">
-        <f>D95 &amp; E95 &amp; "_" &amp; K95</f>
+      <c r="O95" s="4" t="str">
+        <f>D95 &amp; E95 &amp; "_" &amp; L95</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O95" s="4" t="s">
+      <c r="P95" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="P95" s="4" t="str">
+      <c r="Q95" s="4" t="str">
         <f>D95 &amp; E95 &amp; "_" &amp; F95</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
-      <c r="Q95" s="4"/>
-    </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R95" s="4"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -4955,14 +5186,14 @@
       <c r="C96" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -4984,38 +5215,38 @@
       <c r="G97" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="I97" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="I97" s="3" t="s">
+      <c r="J97" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J97" s="3" t="s">
+      <c r="K97" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="L97" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L97" s="3" t="s">
+      <c r="M97" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M97" s="3" t="str">
-        <f>"groupWeapons" &amp; C97 &amp; "_" &amp; K97</f>
+      <c r="N97" s="3" t="str">
+        <f>"groupWeapons" &amp; C97 &amp; "_" &amp; L97</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="N97" s="3" t="str">
-        <f>D97 &amp; E97 &amp; "_" &amp; K97</f>
+      <c r="O97" s="3" t="str">
+        <f>D97 &amp; E97 &amp; "_" &amp; L97</f>
         <v>groupWeaponsT1_Gunslinger</v>
       </c>
-      <c r="O97" s="3" t="s">
+      <c r="P97" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="P97" s="3" t="str">
+      <c r="Q97" s="3" t="str">
         <f>D97 &amp; E97 &amp; "_" &amp; F97</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -5025,14 +5256,14 @@
       <c r="C98" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="I98" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I98" s="3" t="s">
+      <c r="J98" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -5054,35 +5285,35 @@
       <c r="G99" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="I99" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I99" s="3" t="s">
+      <c r="J99" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="K99" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="L99" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L99" s="3" t="s">
+      <c r="M99" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M99" s="3" t="str">
-        <f>"groupWeapons" &amp; C99 &amp; "_" &amp; K99</f>
+      <c r="N99" s="3" t="str">
+        <f>"groupWeapons" &amp; C99 &amp; "_" &amp; L99</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="N99" s="3" t="str">
-        <f>D99 &amp; E99 &amp; "_" &amp; K99</f>
+      <c r="O99" s="3" t="str">
+        <f>D99 &amp; E99 &amp; "_" &amp; L99</f>
         <v>groupWeaponsT2_Gunslinger</v>
       </c>
-      <c r="P99" s="3" t="str">
+      <c r="Q99" s="3" t="str">
         <f>D99 &amp; E99 &amp; "_" &amp; F99</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -5092,14 +5323,14 @@
       <c r="C100" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5121,38 +5352,38 @@
       <c r="G101" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M101" s="3" t="str">
-        <f>"groupWeapons" &amp; C101 &amp; "_" &amp; K101</f>
+      <c r="N101" s="3" t="str">
+        <f>"groupWeapons" &amp; C101 &amp; "_" &amp; L101</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N101" s="3" t="str">
-        <f>D101 &amp; E101 &amp; "_" &amp; K101</f>
+      <c r="O101" s="3" t="str">
+        <f>D101 &amp; E101 &amp; "_" &amp; L101</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="P101" s="3" t="str">
+      <c r="Q101" s="3" t="str">
         <f>D101 &amp; E101 &amp; "_" &amp; F101</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -5162,14 +5393,14 @@
       <c r="C102" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="I102" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="J102" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5191,38 +5422,38 @@
       <c r="G103" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="I103" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="J103" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="K103" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="L103" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L103" s="3" t="s">
+      <c r="M103" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M103" s="3" t="str">
-        <f>"groupWeapons" &amp; C103 &amp; "_" &amp; K103</f>
+      <c r="N103" s="3" t="str">
+        <f>"groupWeapons" &amp; C103 &amp; "_" &amp; L103</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N103" s="3" t="str">
-        <f>D103 &amp; E103 &amp; "_" &amp; K103</f>
+      <c r="O103" s="3" t="str">
+        <f>D103 &amp; E103 &amp; "_" &amp; L103</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O103" s="3" t="s">
+      <c r="P103" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P103" s="3" t="str">
+      <c r="Q103" s="3" t="str">
         <f>D103 &amp; E103 &amp; "_" &amp; F103</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -5232,15 +5463,15 @@
       <c r="C104" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="I104" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="J104" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+    <row r="105" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="13">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -5258,17 +5489,15 @@
       <c r="F105" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="H105" s="4" t="s">
+      <c r="H105" s="12"/>
+      <c r="I105" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="I105" s="4" t="s">
+      <c r="J105" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>172</v>
@@ -5276,16 +5505,19 @@
       <c r="L105" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="N105" s="4" t="str">
-        <f>D105 &amp; E105 &amp; "_" &amp; K105</f>
+      <c r="M105" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="O105" s="4" t="str">
+        <f>D105 &amp; E105 &amp; "_" &amp; L105</f>
         <v>groupWeaponsT3_not ready</v>
       </c>
-      <c r="P105" s="4" t="str">
+      <c r="Q105" s="4" t="str">
         <f>D105 &amp; E105 &amp; "_" &amp; F105</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -5295,14 +5527,14 @@
       <c r="C106" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H106" s="3" t="s">
+      <c r="I106" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="I106" s="3" t="s">
+      <c r="J106" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5324,35 +5556,35 @@
       <c r="G107" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="I107" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I107" s="3" t="s">
+      <c r="J107" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="K107" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="L107" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L107" s="3" t="s">
+      <c r="M107" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M107" s="3" t="str">
-        <f>"groupWeapons" &amp; C107 &amp; "_" &amp; K107</f>
+      <c r="N107" s="3" t="str">
+        <f>"groupWeapons" &amp; C107 &amp; "_" &amp; L107</f>
         <v>groupWeaponsT1_Boomstick</v>
       </c>
-      <c r="N107" s="3" t="str">
-        <f>D107 &amp; E107 &amp; "_" &amp; K107</f>
+      <c r="O107" s="3" t="str">
+        <f>D107 &amp; E107 &amp; "_" &amp; L107</f>
         <v>groupWeaponsT1_Boomstick</v>
       </c>
-      <c r="P107" s="3" t="str">
+      <c r="Q107" s="3" t="str">
         <f>D107 &amp; E107 &amp; "_" &amp; F107</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -5362,14 +5594,14 @@
       <c r="C108" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="I108" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I108" s="3" t="s">
+      <c r="J108" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5391,35 +5623,35 @@
       <c r="G109" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="I109" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="I109" s="3" t="s">
+      <c r="J109" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="K109" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K109" s="3" t="s">
+      <c r="L109" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L109" s="3" t="s">
+      <c r="M109" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M109" s="3" t="str">
-        <f>"groupWeapons" &amp; C109 &amp; "_" &amp; K109</f>
+      <c r="N109" s="3" t="str">
+        <f>"groupWeapons" &amp; C109 &amp; "_" &amp; L109</f>
         <v>groupWeaponsT2_Boomstick</v>
       </c>
-      <c r="N109" s="3" t="str">
-        <f>D109 &amp; E109 &amp; "_" &amp; K109</f>
+      <c r="O109" s="3" t="str">
+        <f>D109 &amp; E109 &amp; "_" &amp; L109</f>
         <v>groupWeaponsT2_Boomstick</v>
       </c>
-      <c r="P109" s="3" t="str">
+      <c r="Q109" s="3" t="str">
         <f>D109 &amp; E109 &amp; "_" &amp; F109</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -5429,14 +5661,14 @@
       <c r="C110" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="I110" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="J110" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5458,35 +5690,35 @@
       <c r="G111" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="I111" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="J111" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J111" s="3" t="s">
+      <c r="K111" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K111" s="3" t="s">
+      <c r="L111" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L111" s="3" t="s">
+      <c r="M111" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M111" s="3" t="str">
-        <f>"groupWeapons" &amp; C111 &amp; "_" &amp; K111</f>
+      <c r="N111" s="3" t="str">
+        <f>"groupWeapons" &amp; C111 &amp; "_" &amp; L111</f>
         <v>groupWeaponsT3_Boomstick</v>
       </c>
-      <c r="N111" s="3" t="str">
-        <f>D111 &amp; E111 &amp; "_" &amp; K111</f>
+      <c r="O111" s="3" t="str">
+        <f>D111 &amp; E111 &amp; "_" &amp; L111</f>
         <v>groupWeaponsT3_Boomstick</v>
       </c>
-      <c r="P111" s="3" t="str">
+      <c r="Q111" s="3" t="str">
         <f>D111 &amp; E111 &amp; "_" &amp; F111</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -5496,14 +5728,14 @@
       <c r="C112" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="I112" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="J112" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5525,35 +5757,35 @@
       <c r="G113" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="I113" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="I113" s="3" t="s">
+      <c r="J113" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J113" s="3" t="s">
+      <c r="K113" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="L113" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L113" s="3" t="s">
+      <c r="M113" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M113" s="3" t="str">
-        <f>"groupWeapons" &amp; C113 &amp; "_" &amp; K113</f>
+      <c r="N113" s="3" t="str">
+        <f>"groupWeapons" &amp; C113 &amp; "_" &amp; L113</f>
         <v>groupWeaponsT4_Boomstick</v>
       </c>
-      <c r="N113" s="3" t="str">
-        <f>D113 &amp; E113 &amp; "_" &amp; K113</f>
+      <c r="O113" s="3" t="str">
+        <f>D113 &amp; E113 &amp; "_" &amp; L113</f>
         <v>groupWeaponsT3_Boomstick</v>
       </c>
-      <c r="P113" s="3" t="str">
+      <c r="Q113" s="3" t="str">
         <f>D113 &amp; E113 &amp; "_" &amp; F113</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -5563,14 +5795,14 @@
       <c r="C114" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="I114" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I114" s="3" t="s">
+      <c r="J114" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5592,35 +5824,35 @@
       <c r="G115" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="I115" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="J115" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="K115" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K115" s="3" t="s">
+      <c r="L115" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="M115" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M115" s="3" t="str">
-        <f>"groupWeapons" &amp; C115 &amp; "_" &amp; K115</f>
+      <c r="N115" s="3" t="str">
+        <f>"groupWeapons" &amp; C115 &amp; "_" &amp; L115</f>
         <v>groupWeaponsT1_Boomstick</v>
       </c>
-      <c r="N115" s="3" t="str">
-        <f>D115 &amp; E115 &amp; "_" &amp; K115</f>
+      <c r="O115" s="3" t="str">
+        <f>D115 &amp; E115 &amp; "_" &amp; L115</f>
         <v>groupWeaponsT1_Boomstick</v>
       </c>
-      <c r="P115" s="3" t="str">
+      <c r="Q115" s="3" t="str">
         <f>D115 &amp; E115 &amp; "_" &amp; F115</f>
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -5630,14 +5862,14 @@
       <c r="C116" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="I116" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="J116" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5659,35 +5891,35 @@
       <c r="G117" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="I117" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="I117" s="3" t="s">
+      <c r="J117" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J117" s="3" t="s">
+      <c r="K117" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="L117" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L117" s="3" t="s">
+      <c r="M117" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M117" s="3" t="str">
-        <f>"groupWeapons" &amp; C117 &amp; "_" &amp; K117</f>
+      <c r="N117" s="3" t="str">
+        <f>"groupWeapons" &amp; C117 &amp; "_" &amp; L117</f>
         <v>groupWeaponsT3_Boomstick</v>
       </c>
-      <c r="N117" s="3" t="str">
-        <f>D117 &amp; E117 &amp; "_" &amp; K117</f>
+      <c r="O117" s="3" t="str">
+        <f>D117 &amp; E117 &amp; "_" &amp; L117</f>
         <v>groupWeaponsT3_Boomstick</v>
       </c>
-      <c r="P117" s="3" t="str">
+      <c r="Q117" s="3" t="str">
         <f>D117 &amp; E117 &amp; "_" &amp; F117</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -5697,14 +5929,14 @@
       <c r="C118" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="I118" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="I118" s="3" t="s">
+      <c r="J118" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5726,38 +5958,38 @@
       <c r="G119" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="I119" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="I119" s="3" t="s">
+      <c r="J119" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J119" s="3" t="s">
+      <c r="K119" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K119" s="3" t="s">
+      <c r="L119" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L119" s="3" t="s">
+      <c r="M119" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M119" s="3" t="str">
-        <f>"groupWeapons" &amp; C119 &amp; "_" &amp; K119</f>
+      <c r="N119" s="3" t="str">
+        <f>"groupWeapons" &amp; C119 &amp; "_" &amp; L119</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="N119" s="3" t="str">
-        <f>D119 &amp; E119 &amp; "_" &amp; K119</f>
+      <c r="O119" s="3" t="str">
+        <f>D119 &amp; E119 &amp; "_" &amp; L119</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O119" s="3" t="s">
+      <c r="P119" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="P119" s="3" t="str">
+      <c r="Q119" s="3" t="str">
         <f>D119 &amp; E119 &amp; "_" &amp; F119</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -5767,14 +5999,14 @@
       <c r="C120" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H120" s="3" t="s">
+      <c r="I120" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="I120" s="3" t="s">
+      <c r="J120" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -5796,38 +6028,38 @@
       <c r="G121" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="I121" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="J121" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="K121" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="L121" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="M121" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M121" s="3" t="str">
-        <f>"groupWeapons" &amp; C121 &amp; "_" &amp; K121</f>
+      <c r="N121" s="3" t="str">
+        <f>"groupWeapons" &amp; C121 &amp; "_" &amp; L121</f>
         <v>groupWeaponsT4_Gunslinger</v>
       </c>
-      <c r="N121" s="3" t="str">
-        <f>D121 &amp; E121 &amp; "_" &amp; K121</f>
+      <c r="O121" s="3" t="str">
+        <f>D121 &amp; E121 &amp; "_" &amp; L121</f>
         <v>groupWeaponsT3_Gunslinger</v>
       </c>
-      <c r="O121" s="3" t="s">
+      <c r="P121" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="P121" s="3" t="str">
+      <c r="Q121" s="3" t="str">
         <f>D121 &amp; E121 &amp; "_" &amp; F121</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -5837,14 +6069,14 @@
       <c r="C122" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H122" s="3" t="s">
+      <c r="I122" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="J122" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -5866,35 +6098,35 @@
       <c r="G123" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H123" s="3" t="s">
+      <c r="I123" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="J123" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J123" s="3" t="s">
+      <c r="K123" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="K123" s="3" t="s">
+      <c r="L123" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L123" s="3" t="s">
+      <c r="M123" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="M123" s="5" t="str">
-        <f>"groupWeapons" &amp; C123 &amp; "_" &amp; K123</f>
+      <c r="N123" s="5" t="str">
+        <f>"groupWeapons" &amp; C123 &amp; "_" &amp; L123</f>
         <v>groupWeaponsT3_TBD</v>
       </c>
-      <c r="N123" s="5" t="s">
+      <c r="O123" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="O123" s="5"/>
-      <c r="P123" s="3" t="str">
+      <c r="P123" s="5"/>
+      <c r="Q123" s="3" t="str">
         <f>D123 &amp; E123 &amp; "_" &amp; F123</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5904,14 +6136,14 @@
       <c r="C124" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="I124" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="J124" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -5933,32 +6165,32 @@
       <c r="G125" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="I125" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="J125" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K125" s="3" t="s">
+      <c r="L125" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="L125" s="3" t="s">
+      <c r="M125" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M125" s="3" t="str">
-        <f>"groupWeapons" &amp; C125 &amp; "_" &amp; K125</f>
+      <c r="N125" s="3" t="str">
+        <f>"groupWeapons" &amp; C125 &amp; "_" &amp; L125</f>
         <v>groupWeaponsT2_Demolitionist</v>
       </c>
-      <c r="N125" s="3" t="str">
-        <f>D125 &amp; E125 &amp; "_" &amp; K125</f>
+      <c r="O125" s="3" t="str">
+        <f>D125 &amp; E125 &amp; "_" &amp; L125</f>
         <v>groupWeaponsT2_Demolitionist</v>
       </c>
-      <c r="P125" s="3" t="str">
+      <c r="Q125" s="3" t="str">
         <f>D125 &amp; E125 &amp; "_" &amp; F125</f>
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -5968,14 +6200,14 @@
       <c r="C126" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="I126" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="I126" s="3" t="s">
+      <c r="J126" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -5997,32 +6229,32 @@
       <c r="G127" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="H127" s="3" t="s">
+      <c r="I127" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="J127" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="K127" s="3" t="s">
+      <c r="L127" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="L127" s="3" t="s">
+      <c r="M127" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M127" s="3" t="str">
-        <f>"groupWeapons" &amp; C127 &amp; "_" &amp; K127</f>
+      <c r="N127" s="3" t="str">
+        <f>"groupWeapons" &amp; C127 &amp; "_" &amp; L127</f>
         <v>groupWeaponsT3_Demolitionist01</v>
       </c>
-      <c r="N127" s="3" t="str">
-        <f>D127 &amp; E127 &amp; "_" &amp; K127</f>
+      <c r="O127" s="3" t="str">
+        <f>D127 &amp; E127 &amp; "_" &amp; L127</f>
         <v>groupWeaponsT3_Demolitionist01</v>
       </c>
-      <c r="P127" s="3" t="str">
+      <c r="Q127" s="3" t="str">
         <f>D127 &amp; E127 &amp; "_" &amp; F127</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -6032,14 +6264,14 @@
       <c r="C128" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="I128" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="J128" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -6061,46 +6293,46 @@
       <c r="G129" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="I129" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="J129" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="K129" s="3" t="s">
+      <c r="L129" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="L129" s="3" t="s">
+      <c r="M129" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M129" s="3" t="str">
-        <f>"groupWeapons" &amp; C129 &amp; "_" &amp; K129</f>
+      <c r="N129" s="3" t="str">
+        <f>"groupWeapons" &amp; C129 &amp; "_" &amp; L129</f>
         <v>groupWeaponsT3_Demolitionist01</v>
       </c>
-      <c r="N129" s="3" t="str">
-        <f>D129 &amp; E129 &amp; "_" &amp; K129</f>
+      <c r="O129" s="3" t="str">
+        <f>D129 &amp; E129 &amp; "_" &amp; L129</f>
         <v>groupWeaponsT3_Demolitionist01</v>
       </c>
-      <c r="P129" s="3" t="str">
+      <c r="Q129" s="3" t="str">
         <f>D129 &amp; E129 &amp; "_" &amp; F129</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="I130" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="I130" s="3" t="s">
+      <c r="J130" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -6122,49 +6354,49 @@
       <c r="G131" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="I131" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="I131" s="3" t="s">
+      <c r="J131" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="K131" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K131" s="3" t="s">
+      <c r="L131" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L131" s="3" t="s">
+      <c r="M131" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M131" s="3" t="str">
-        <f>"groupWeapons" &amp; C131 &amp; "_" &amp; K131</f>
+      <c r="N131" s="3" t="str">
+        <f>"groupWeapons" &amp; C131 &amp; "_" &amp; L131</f>
         <v>groupWeaponsT5_Machinegunner</v>
       </c>
-      <c r="N131" s="3" t="str">
-        <f>D131 &amp; E131 &amp; "_" &amp; K131</f>
+      <c r="O131" s="3" t="str">
+        <f>D131 &amp; E131 &amp; "_" &amp; L131</f>
         <v>groupWeaponsT3_Machinegunner</v>
       </c>
-      <c r="P131" s="3" t="str">
+      <c r="Q131" s="3" t="str">
         <f>D131 &amp; E131 &amp; "_" &amp; F131</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="I132" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="I132" s="3" t="s">
+      <c r="J132" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6186,35 +6418,35 @@
       <c r="G133" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="I133" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="I133" s="3" t="s">
+      <c r="J133" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K133" s="5" t="s">
+      <c r="L133" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L133" s="3" t="s">
+      <c r="M133" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="M133" s="3" t="str">
-        <f>"groupWeapons" &amp; C133 &amp; "_" &amp; K133</f>
+      <c r="N133" s="3" t="str">
+        <f>"groupWeapons" &amp; C133 &amp; "_" &amp; L133</f>
         <v>groupWeaponsT5_Boomstick</v>
       </c>
-      <c r="N133" s="5" t="s">
+      <c r="O133" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="O133" s="5"/>
-      <c r="P133" s="3" t="str">
+      <c r="P133" s="5"/>
+      <c r="Q133" s="3" t="str">
         <f>D133 &amp; E133 &amp; "_" &amp; F133</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -6224,14 +6456,14 @@
       <c r="C134" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="I134" s="3" t="s">
+      <c r="J134" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6253,49 +6485,49 @@
       <c r="G135" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="I135" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="I135" s="3" t="s">
+      <c r="J135" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J135" s="3" t="s">
+      <c r="K135" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K135" s="3" t="s">
+      <c r="L135" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="L135" s="3" t="s">
+      <c r="M135" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M135" s="3" t="str">
-        <f>"groupWeapons" &amp; C135 &amp; "_" &amp; K135</f>
+      <c r="N135" s="3" t="str">
+        <f>"groupWeapons" &amp; C135 &amp; "_" &amp; L135</f>
         <v>groupWeaponsT4_Archery</v>
       </c>
-      <c r="N135" s="5" t="s">
+      <c r="O135" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="O135" s="5"/>
-      <c r="P135" s="3" t="str">
+      <c r="P135" s="5"/>
+      <c r="Q135" s="3" t="str">
         <f>D135 &amp; E135 &amp; "_" &amp; F135</f>
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="I136" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="I136" s="3" t="s">
+      <c r="J136" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -6317,35 +6549,35 @@
       <c r="G137" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="I137" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="I137" s="3" t="s">
+      <c r="J137" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J137" s="3" t="s">
+      <c r="K137" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="K137" s="9" t="s">
+      <c r="L137" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="L137" s="3" t="s">
+      <c r="M137" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M137" s="3" t="str">
-        <f>"groupWeapons" &amp; C137 &amp; "_" &amp; K137</f>
+      <c r="N137" s="3" t="str">
+        <f>"groupWeapons" &amp; C137 &amp; "_" &amp; L137</f>
         <v>groupWeaponsT0_DeadEye</v>
       </c>
-      <c r="N137" s="3" t="str">
-        <f>D137 &amp; E137 &amp; "_" &amp; K137</f>
+      <c r="O137" s="3" t="str">
+        <f>D137 &amp; E137 &amp; "_" &amp; L137</f>
         <v>groupWeaponsT0_DeadEye</v>
       </c>
-      <c r="P137" s="3" t="str">
+      <c r="Q137" s="3" t="str">
         <f>D137 &amp; E137 &amp; "_" &amp; F137</f>
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -6355,14 +6587,14 @@
       <c r="C138" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="I138" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6384,34 +6616,34 @@
       <c r="G139" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="I139" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="I139" s="3" t="s">
+      <c r="J139" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="M139" s="3" t="str">
-        <f>"groupWeapons" &amp; C139 &amp; "_" &amp; K139</f>
+      <c r="N139" s="3" t="str">
+        <f>"groupWeapons" &amp; C139 &amp; "_" &amp; L139</f>
         <v>groupWeaponsT4_Deep Cuts</v>
       </c>
-      <c r="N139" s="3" t="s">
+      <c r="O139" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="P139" s="3" t="str">
+      <c r="Q139" s="3" t="str">
         <f>D139 &amp; E139 &amp; "_" &amp; F139</f>
         <v>groupWeaponsT2_Melee</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -6421,14 +6653,14 @@
       <c r="C140" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H140" s="3" t="s">
+      <c r="I140" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="I140" s="3" t="s">
+      <c r="J140" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6450,34 +6682,34 @@
       <c r="G141" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H141" s="3" t="s">
+      <c r="I141" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="I141" s="3" t="s">
+      <c r="J141" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J141" s="3" t="s">
+      <c r="K141" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K141" s="3" t="s">
+      <c r="L141" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L141" s="3" t="s">
+      <c r="M141" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="M141" s="3" t="str">
-        <f>"groupWeapons" &amp; C141 &amp; "_" &amp; K141</f>
+      <c r="N141" s="3" t="str">
+        <f>"groupWeapons" &amp; C141 &amp; "_" &amp; L141</f>
         <v>groupWeaponsT4_Skull Crusher</v>
       </c>
-      <c r="N141" s="3" t="s">
+      <c r="O141" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="P141" s="3" t="str">
+      <c r="Q141" s="3" t="str">
         <f>D141 &amp; E141 &amp; "_" &amp; F141</f>
         <v>groupWeaponsT2_Melee</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -6487,14 +6719,14 @@
       <c r="C142" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H142" s="3" t="s">
+      <c r="I142" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="I142" s="3" t="s">
+      <c r="J142" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6516,41 +6748,38 @@
       <c r="G143" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H143" s="3" t="s">
+      <c r="I143" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I143" s="3" t="s">
+      <c r="J143" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J143" s="3" t="s">
+      <c r="K143" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K143" s="3" t="s">
+      <c r="L143" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="L143" s="3" t="s">
+      <c r="M143" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M143" s="3" t="str">
-        <f>"groupWeapons" &amp; C143 &amp; "_" &amp; K143</f>
+      <c r="N143" s="3" t="str">
+        <f>"groupWeapons" &amp; C143 &amp; "_" &amp; L143</f>
         <v>groupWeaponsT4_Spear Master</v>
       </c>
-      <c r="N143" s="3" t="s">
+      <c r="O143" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="P143" s="3" t="str">
+      <c r="Q143" s="3" t="str">
         <f>D143 &amp; E143 &amp; "_" &amp; F143</f>
         <v>groupWeaponsT2_Melee</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="DeadEye"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}"/>
+  <conditionalFormatting sqref="G1:H1048576">
+    <cfRule type="uniqueValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6560,336 +6789,336 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="11"/>
-    <col min="2" max="2" width="47.33203125" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="8.88671875" style="9"/>
+    <col min="2" max="2" width="47.33203125" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
+      <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
+      <c r="A17" s="9">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
+      <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
+      <c r="A23" s="9">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+      <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
+      <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="11">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="9" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="11">
+      <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="11">
+      <c r="A30" s="9">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="11">
+      <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="11">
+      <c r="A32" s="9">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="11">
+      <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
+      <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="11">
+      <c r="A35" s="9">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="11">
+      <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="11">
+      <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="11">
+      <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="11">
+      <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="9" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="11">
+      <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="9" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="11">
+      <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="9" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="11">
+      <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="9" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="11">
+      <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="9" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="11">
+      <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="9" t="s">
         <v>389</v>
       </c>
     </row>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D165FC-2B54-4E96-AFF5-C2B5B2F3A8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9D018D-89C7-442D-ACB3-92F9308F1BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -1303,7 +1303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1324,13 +1324,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1656,6 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1665,7 +1665,7 @@
     <col min="5" max="5" width="5" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="41.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" style="3" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="16.77734375" style="3" customWidth="1"/>
     <col min="10" max="10" width="22" style="3" customWidth="1"/>
     <col min="11" max="11" width="11.44140625" style="3" customWidth="1"/>
@@ -1701,7 +1701,7 @@
       <c r="G1" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>390</v>
       </c>
       <c r="I1" s="6" t="s">
@@ -1735,7 +1735,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1745,7 +1745,7 @@
       <c r="C2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="3" t="s">
         <v>193</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -1755,7 +1755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1777,7 +1777,7 @@
       <c r="G3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="3" t="s">
         <v>253</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -1811,7 +1811,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1821,7 +1821,7 @@
       <c r="C4" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="3" t="s">
         <v>173</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -1834,7 +1834,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1853,10 +1853,10 @@
       <c r="F5" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="3" t="s">
         <v>213</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -1890,7 +1890,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="C6" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="3" t="s">
         <v>175</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -1913,7 +1913,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1932,10 +1932,10 @@
       <c r="F7" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="3" t="s">
         <v>239</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -1969,7 +1969,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1979,7 +1979,7 @@
       <c r="C8" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="3" t="s">
         <v>267</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -1992,7 +1992,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2011,10 +2011,10 @@
       <c r="F9" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="3" t="s">
         <v>195</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -2048,7 +2048,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2058,7 +2058,7 @@
       <c r="C10" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="3" t="s">
         <v>197</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -2071,7 +2071,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2090,10 +2090,10 @@
       <c r="F11" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="3" t="s">
         <v>251</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -2127,7 +2127,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2137,7 +2137,7 @@
       <c r="C12" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="3" t="s">
         <v>255</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -2150,7 +2150,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2169,10 +2169,10 @@
       <c r="F13" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="3" t="s">
         <v>221</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -2206,7 +2206,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2216,7 +2216,7 @@
       <c r="C14" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="3" t="s">
         <v>285</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -2229,7 +2229,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2248,10 +2248,10 @@
       <c r="F15" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="3" t="s">
         <v>277</v>
       </c>
       <c r="I15" s="3" t="s">
@@ -2285,7 +2285,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2295,7 +2295,7 @@
       <c r="C16" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="3" t="s">
         <v>207</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -2308,7 +2308,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="G17" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="3" t="s">
         <v>177</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -2364,7 +2364,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="C18" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="3" t="s">
         <v>235</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -2387,7 +2387,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2406,10 +2406,10 @@
       <c r="F19" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="3" t="s">
         <v>241</v>
       </c>
       <c r="I19" s="3" t="s">
@@ -2443,7 +2443,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="C20" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="3" t="s">
         <v>269</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -2466,7 +2466,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2485,10 +2485,10 @@
       <c r="F21" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="3" t="s">
         <v>205</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -2519,7 +2519,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="C22" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="3" t="s">
         <v>295</v>
       </c>
       <c r="I22" s="3" t="s">
@@ -2561,7 +2561,7 @@
       <c r="G23" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="3" t="s">
         <v>247</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -2592,7 +2592,7 @@
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -2602,7 +2602,7 @@
       <c r="C24" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="3" t="s">
         <v>183</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -2634,7 +2634,7 @@
       <c r="G25" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="3" t="s">
         <v>227</v>
       </c>
       <c r="I25" s="3" t="s">
@@ -2668,7 +2668,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -2678,7 +2678,7 @@
       <c r="C26" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="3" t="s">
         <v>199</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -2710,7 +2710,7 @@
       <c r="G27" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="3" t="s">
         <v>257</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -2741,7 +2741,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="C28" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="3" t="s">
         <v>279</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -2783,7 +2783,7 @@
       <c r="G29" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="3" t="s">
         <v>209</v>
       </c>
       <c r="I29" s="3" t="s">
@@ -2814,7 +2814,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="C30" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="3" t="s">
         <v>237</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -2856,7 +2856,7 @@
       <c r="G31" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -2890,7 +2890,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -2900,7 +2900,7 @@
       <c r="C32" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="3" t="s">
         <v>243</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -2932,7 +2932,7 @@
       <c r="G33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="3" t="s">
         <v>189</v>
       </c>
       <c r="I33" s="3" t="s">
@@ -2966,7 +2966,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2976,7 +2976,7 @@
       <c r="C34" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="3" t="s">
         <v>271</v>
       </c>
       <c r="I34" s="3" t="s">
@@ -3008,7 +3008,7 @@
       <c r="G35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="3" t="s">
         <v>297</v>
       </c>
       <c r="I35" s="3" t="s">
@@ -3039,7 +3039,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="C36" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="3" t="s">
         <v>185</v>
       </c>
       <c r="I36" s="3" t="s">
@@ -3081,7 +3081,7 @@
       <c r="G37" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="3" t="s">
         <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
@@ -3112,7 +3112,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3122,7 +3122,7 @@
       <c r="C38" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="3" t="s">
         <v>229</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -3154,7 +3154,7 @@
       <c r="G39" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="3" t="s">
         <v>217</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -3188,7 +3188,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3198,7 +3198,7 @@
       <c r="C40" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="3" t="s">
         <v>201</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -3230,7 +3230,7 @@
       <c r="G41" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="3" t="s">
         <v>289</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -3264,7 +3264,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3274,7 +3274,7 @@
       <c r="C42" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="3" t="s">
         <v>299</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -3334,7 +3334,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3344,7 +3344,7 @@
       <c r="C44" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="3" t="s">
         <v>259</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -3376,7 +3376,7 @@
       <c r="G45" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="3" t="s">
         <v>223</v>
       </c>
       <c r="I45" s="3" t="s">
@@ -3410,7 +3410,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="C46" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="3" t="s">
         <v>287</v>
       </c>
       <c r="I46" s="3" t="s">
@@ -3452,7 +3452,7 @@
       <c r="G47" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="3" t="s">
         <v>293</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -3483,7 +3483,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="C48" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="3" t="s">
         <v>281</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -3525,7 +3525,7 @@
       <c r="G49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="3" t="s">
         <v>211</v>
       </c>
       <c r="I49" s="3" t="s">
@@ -3556,7 +3556,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="C50" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -3576,7 +3576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3598,7 +3598,7 @@
       <c r="G51" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="3" t="s">
         <v>181</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -3629,7 +3629,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3639,7 +3639,7 @@
       <c r="C52" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H52" s="3" t="s">
         <v>245</v>
       </c>
       <c r="I52" s="3" t="s">
@@ -3649,7 +3649,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3671,7 +3671,7 @@
       <c r="G53" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="3" t="s">
         <v>305</v>
       </c>
       <c r="I53" s="3" t="s">
@@ -3702,7 +3702,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3712,7 +3712,7 @@
       <c r="C54" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="3" t="s">
         <v>191</v>
       </c>
       <c r="I54" s="3" t="s">
@@ -3722,7 +3722,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3744,7 +3744,7 @@
       <c r="G55" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="3" t="s">
         <v>291</v>
       </c>
       <c r="I55" s="3" t="s">
@@ -3775,7 +3775,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="G57" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="3" t="s">
         <v>273</v>
       </c>
       <c r="I57" s="3" t="s">
@@ -3845,7 +3845,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -3855,7 +3855,7 @@
       <c r="C58" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="3" t="s">
         <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
@@ -3865,7 +3865,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3887,7 +3887,7 @@
       <c r="G59" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="3" t="s">
         <v>219</v>
       </c>
       <c r="I59" s="3" t="s">
@@ -3918,7 +3918,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="C60" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H60" s="3" t="s">
         <v>233</v>
       </c>
       <c r="I60" s="3" t="s">
@@ -3938,7 +3938,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="G61" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="3" t="s">
         <v>231</v>
       </c>
       <c r="I61" s="3" t="s">
@@ -3991,7 +3991,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4001,7 +4001,7 @@
       <c r="C62" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H62" s="10" t="s">
+      <c r="H62" s="3" t="s">
         <v>203</v>
       </c>
       <c r="I62" s="3" t="s">
@@ -4011,7 +4011,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="C64" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H64" s="10" t="s">
+      <c r="H64" s="3" t="s">
         <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
@@ -4081,7 +4081,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -4103,7 +4103,7 @@
       <c r="G65" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="3" t="s">
         <v>225</v>
       </c>
       <c r="I65" s="3" t="s">
@@ -4134,7 +4134,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -4144,7 +4144,7 @@
       <c r="C66" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H66" s="10" t="s">
+      <c r="H66" s="3" t="s">
         <v>283</v>
       </c>
       <c r="I66" s="3" t="s">
@@ -4154,7 +4154,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="G67" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="3" t="s">
         <v>301</v>
       </c>
       <c r="I67" s="3" t="s">
@@ -4207,7 +4207,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4217,7 +4217,7 @@
       <c r="C68" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="3" t="s">
         <v>303</v>
       </c>
       <c r="I68" s="3" t="s">
@@ -4227,7 +4227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4249,7 +4249,7 @@
       <c r="G69" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="3" t="s">
         <v>307</v>
       </c>
       <c r="I69" s="3" t="s">
@@ -4280,7 +4280,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="C70" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="3" t="s">
         <v>309</v>
       </c>
       <c r="I70" s="3" t="s">
@@ -4300,7 +4300,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4322,7 +4322,7 @@
       <c r="G71" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="3" t="s">
         <v>311</v>
       </c>
       <c r="I71" s="3" t="s">
@@ -4353,7 +4353,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4363,7 +4363,7 @@
       <c r="C72" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="3" t="s">
         <v>313</v>
       </c>
       <c r="I72" s="3" t="s">
@@ -4373,7 +4373,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -5049,8 +5049,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A93" s="13">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="12">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
@@ -5068,10 +5068,10 @@
       <c r="F93" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G93" s="14" t="s">
+      <c r="G93" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="H93" s="12"/>
+      <c r="H93" s="11"/>
       <c r="I93" s="3" t="s">
         <v>264</v>
       </c>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="R93" s="4"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -5121,8 +5121,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A95" s="13">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="12">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
@@ -5140,10 +5140,10 @@
       <c r="F95" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G95" s="14" t="s">
+      <c r="G95" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H95" s="12"/>
+      <c r="H95" s="11"/>
       <c r="I95" s="3" t="s">
         <v>266</v>
       </c>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="R95" s="4"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -5470,8 +5470,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="13">
+    <row r="105" spans="1:17" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="12">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
@@ -5489,10 +5489,10 @@
       <c r="F105" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="G105" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="H105" s="12"/>
+      <c r="H105" s="11"/>
       <c r="I105" s="4" t="s">
         <v>276</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>groupWeaponsT1_Ranged</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>groupWeaponsT2_Ranged</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>groupWeaponsT3_Ranged</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>groupWeaponsT0_Ranged</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>groupWeaponsT2_Melee</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>groupWeaponsT2_Melee</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6776,7 +6776,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}"/>
+  <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val=".45 ACP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="G1:H1048576">
     <cfRule type="uniqueValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9D018D-89C7-442D-ACB3-92F9308F1BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77ADF1B-0735-482C-A11B-A38D46400B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77ADF1B-0735-482C-A11B-A38D46400B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD531FD-E5B4-446A-B9C4-E4DC4CDCE491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -2539,7 +2539,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6777,9 +6777,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
-    <filterColumn colId="10">
+    <filterColumn colId="11">
       <filters>
-        <filter val=".45 ACP"/>
+        <filter val="Boomstick"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD531FD-E5B4-446A-B9C4-E4DC4CDCE491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44C8BE8-68EA-4C49-9920-38ED70CB106A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -5534,7 +5534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6779,7 +6779,9 @@
   <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
     <filterColumn colId="11">
       <filters>
-        <filter val="Boomstick"/>
+        <filter val="Deep Cuts"/>
+        <filter val="Skull Crusher"/>
+        <filter val="Spear Master"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Reference/loca_table.xlsx
+++ b/Reference/loca_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_github\gunpack\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44C8BE8-68EA-4C49-9920-38ED70CB106A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A2F70-C586-4C16-9703-0DCDA93DE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{36B2EE77-78C9-4D65-B948-4FE9362E1906}"/>
   </bookViews>
@@ -24,6 +24,16 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1755,7 +1765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2308,7 +2318,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3430,7 +3440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3503,7 +3513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3576,7 +3586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3649,7 +3659,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3722,7 +3732,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3792,7 +3802,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -3865,7 +3875,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3938,7 +3948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4011,7 +4021,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -6527,7 +6537,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -6594,7 +6604,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6660,7 +6670,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6726,7 +6736,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6779,9 +6789,7 @@
   <autoFilter ref="A1:R143" xr:uid="{15D4084D-40A0-4718-BDD7-5AA00735FE8A}">
     <filterColumn colId="11">
       <filters>
-        <filter val="Deep Cuts"/>
-        <filter val="Skull Crusher"/>
-        <filter val="Spear Master"/>
+        <filter val="DeadEye"/>
       </filters>
     </filterColumn>
   </autoFilter>
